--- a/data/modelamiento/diagnostico_modelamiento.xlsx
+++ b/data/modelamiento/diagnostico_modelamiento.xlsx
@@ -403,7 +403,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -513,10 +513,10 @@
         <v>48</v>
       </c>
       <c r="E2">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="F2">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -545,10 +545,10 @@
         <v>52</v>
       </c>
       <c r="E3">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="F3">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -577,10 +577,10 @@
         <v>13</v>
       </c>
       <c r="E4">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="F4">
-        <v>-18</v>
+        <v>-13</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -609,10 +609,10 @@
         <v>48</v>
       </c>
       <c r="E5">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="F5">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -641,10 +641,10 @@
         <v>645</v>
       </c>
       <c r="E6">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="F6">
-        <v>627</v>
+        <v>632</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -673,10 +673,10 @@
         <v>685</v>
       </c>
       <c r="E7">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="F7">
-        <v>667</v>
+        <v>672</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         <v>118</v>
       </c>
       <c r="E8">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="F8">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -737,10 +737,10 @@
         <v>645</v>
       </c>
       <c r="E9">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="F9">
-        <v>627</v>
+        <v>632</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -897,14 +897,14 @@
         <v>30</v>
       </c>
       <c r="E14">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="F14">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>alerta_gl_ajustado</t>
+          <t>aceptable_para_small_data</t>
         </is>
       </c>
       <c r="H14" t="b">
@@ -929,10 +929,10 @@
         <v>34</v>
       </c>
       <c r="E15">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="F15">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -961,10 +961,10 @@
         <v>13</v>
       </c>
       <c r="E16">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="F16">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -993,14 +993,14 @@
         <v>30</v>
       </c>
       <c r="E17">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="F17">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>alerta_gl_ajustado</t>
+          <t>aceptable_para_small_data</t>
         </is>
       </c>
       <c r="H17" t="b">
@@ -1163,7 +1163,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="B2">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>alerta_gl_ajustado</t>
+          <t>critico_gl_insuficiente</t>
         </is>
       </c>
       <c r="B3">
@@ -1201,20 +1201,10 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>critico_gl_insuficiente</t>
+          <t>critico_muy_pocos_datos</t>
         </is>
       </c>
       <c r="B4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>critico_muy_pocos_datos</t>
-        </is>
-      </c>
-      <c r="B5">
         <v>1</v>
       </c>
     </row>
